--- a/local-qa/eval/Evaluation_Scoresheet.xlsx
+++ b/local-qa/eval/Evaluation_Scoresheet.xlsx
@@ -714,19 +714,19 @@
         </is>
       </c>
       <c r="B2" s="6">
-        <f>COUNTIF('Test cases'!$B$3:$B$20,"A: Unstructured")</f>
+        <f>COUNTIF('Test cases'!$B$3:$B$21,"A: Unstructured")</f>
         <v/>
       </c>
       <c r="C2" s="6">
-        <f>COUNTIF('Test cases'!$B$3:$B$20,"B: Sales")</f>
+        <f>COUNTIF('Test cases'!$B$3:$B$21,"B: Sales")</f>
         <v/>
       </c>
       <c r="D2" s="6">
-        <f>COUNTIF('Test cases'!$B$3:$B$20,"Cross-use-case")</f>
+        <f>COUNTIF('Test cases'!$B$3:$B$21,"Cross-use-case")</f>
         <v/>
       </c>
       <c r="E2" s="6">
-        <f>COUNTA('Test cases'!$A$3:$A$20)</f>
+        <f>COUNTA('Test cases'!$A$3:$A$21)</f>
         <v/>
       </c>
       <c r="F2" s="6" t="inlineStr"/>
@@ -738,19 +738,19 @@
         </is>
       </c>
       <c r="B3" s="6">
-        <f>COUNTIFS('Test cases'!$B$3:$B$20,"A: Unstructured",'Test cases'!$J$3:$J$20,"&lt;&gt;")</f>
+        <f>COUNTIFS('Test cases'!$B$3:$B$21,"A: Unstructured",'Test cases'!$J$3:$J$21,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="C3" s="6">
-        <f>COUNTIFS('Test cases'!$B$3:$B$20,"B: Sales",'Test cases'!$J$3:$J$20,"&lt;&gt;")</f>
+        <f>COUNTIFS('Test cases'!$B$3:$B$21,"B: Sales",'Test cases'!$J$3:$J$21,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D3" s="6">
-        <f>COUNTIFS('Test cases'!$B$3:$B$20,"Cross-use-case",'Test cases'!$J$3:$J$20,"&lt;&gt;")</f>
+        <f>COUNTIFS('Test cases'!$B$3:$B$21,"Cross-use-case",'Test cases'!$J$3:$J$21,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="E3" s="6">
-        <f>COUNT('Test cases'!$J$3:$J$20)</f>
+        <f>COUNT('Test cases'!$J$3:$J$21)</f>
         <v/>
       </c>
       <c r="F3" s="6" t="inlineStr"/>
@@ -762,19 +762,19 @@
         </is>
       </c>
       <c r="B4" s="6">
-        <f>COUNTIFS('Test cases'!$B$3:$B$20,"A: Unstructured",'Test cases'!$J$3:$J$20,2)</f>
+        <f>COUNTIFS('Test cases'!$B$3:$B$21,"A: Unstructured",'Test cases'!$J$3:$J$21,2)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIFS('Test cases'!$B$3:$B$20,"B: Sales",'Test cases'!$J$3:$J$20,2)</f>
+        <f>COUNTIFS('Test cases'!$B$3:$B$21,"B: Sales",'Test cases'!$J$3:$J$21,2)</f>
         <v/>
       </c>
       <c r="D4" s="6">
-        <f>COUNTIFS('Test cases'!$B$3:$B$20,"Cross-use-case",'Test cases'!$J$3:$J$20,2)</f>
+        <f>COUNTIFS('Test cases'!$B$3:$B$21,"Cross-use-case",'Test cases'!$J$3:$J$21,2)</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Test cases'!$J$3:$J$20,2)</f>
+        <f>COUNTIF('Test cases'!$J$3:$J$21,2)</f>
         <v/>
       </c>
       <c r="F4" s="6" t="inlineStr"/>
@@ -786,19 +786,19 @@
         </is>
       </c>
       <c r="B5" s="7">
-        <f>IFERROR(SUMIFS('Test cases'!$J$3:$J$20,'Test cases'!$B$3:$B$20,"A: Unstructured")/(2*COUNTIFS('Test cases'!$B$3:$B$20,"A: Unstructured",'Test cases'!$J$3:$J$20,"&lt;&gt;")),"")</f>
+        <f>IFERROR(SUMIFS('Test cases'!$J$3:$J$21,'Test cases'!$B$3:$B$21,"A: Unstructured")/(2*COUNTIFS('Test cases'!$B$3:$B$21,"A: Unstructured",'Test cases'!$J$3:$J$21,"&lt;&gt;")),"")</f>
         <v/>
       </c>
       <c r="C5" s="7">
-        <f>IFERROR(SUMIFS('Test cases'!$J$3:$J$20,'Test cases'!$B$3:$B$20,"B: Sales")/(2*COUNTIFS('Test cases'!$B$3:$B$20,"B: Sales",'Test cases'!$J$3:$J$20,"&lt;&gt;")),"")</f>
+        <f>IFERROR(SUMIFS('Test cases'!$J$3:$J$21,'Test cases'!$B$3:$B$21,"B: Sales")/(2*COUNTIFS('Test cases'!$B$3:$B$21,"B: Sales",'Test cases'!$J$3:$J$21,"&lt;&gt;")),"")</f>
         <v/>
       </c>
       <c r="D5" s="7">
-        <f>IFERROR(SUMIFS('Test cases'!$J$3:$J$20,'Test cases'!$B$3:$B$20,"Cross-use-case")/(2*COUNTIFS('Test cases'!$B$3:$B$20,"Cross-use-case",'Test cases'!$J$3:$J$20,"&lt;&gt;")),"")</f>
+        <f>IFERROR(SUMIFS('Test cases'!$J$3:$J$21,'Test cases'!$B$3:$B$21,"Cross-use-case")/(2*COUNTIFS('Test cases'!$B$3:$B$21,"Cross-use-case",'Test cases'!$J$3:$J$21,"&lt;&gt;")),"")</f>
         <v/>
       </c>
       <c r="E5" s="7">
-        <f>IFERROR(SUM('Test cases'!$J$3:$J$20)/(2*COUNT('Test cases'!$J$3:$J$20)),"")</f>
+        <f>IFERROR(SUM('Test cases'!$J$3:$J$21)/(2*COUNT('Test cases'!$J$3:$J$21)),"")</f>
         <v/>
       </c>
       <c r="F5" s="6" t="inlineStr">
@@ -814,19 +814,19 @@
         </is>
       </c>
       <c r="B6" s="7">
-        <f>IFERROR(COUNTIFS('Test cases'!$B$3:$B$20,"A: Unstructured",'Test cases'!$K$3:$K$20,"Y")/COUNTIFS('Test cases'!$B$3:$B$20,"A: Unstructured",'Test cases'!$K$3:$K$20,"?*"),"")</f>
+        <f>IFERROR(COUNTIFS('Test cases'!$B$3:$B$21,"A: Unstructured",'Test cases'!$K$3:$K$21,"Y")/COUNTIFS('Test cases'!$B$3:$B$21,"A: Unstructured",'Test cases'!$K$3:$K$21,"?*"),"")</f>
         <v/>
       </c>
       <c r="C6" s="7">
-        <f>IFERROR(COUNTIFS('Test cases'!$B$3:$B$20,"B: Sales",'Test cases'!$K$3:$K$20,"Y")/COUNTIFS('Test cases'!$B$3:$B$20,"B: Sales",'Test cases'!$K$3:$K$20,"?*"),"")</f>
+        <f>IFERROR(COUNTIFS('Test cases'!$B$3:$B$21,"B: Sales",'Test cases'!$K$3:$K$21,"Y")/COUNTIFS('Test cases'!$B$3:$B$21,"B: Sales",'Test cases'!$K$3:$K$21,"?*"),"")</f>
         <v/>
       </c>
       <c r="D6" s="7">
-        <f>IFERROR(COUNTIFS('Test cases'!$B$3:$B$20,"Cross-use-case",'Test cases'!$K$3:$K$20,"Y")/COUNTIFS('Test cases'!$B$3:$B$20,"Cross-use-case",'Test cases'!$K$3:$K$20,"?*"),"")</f>
+        <f>IFERROR(COUNTIFS('Test cases'!$B$3:$B$21,"Cross-use-case",'Test cases'!$K$3:$K$21,"Y")/COUNTIFS('Test cases'!$B$3:$B$21,"Cross-use-case",'Test cases'!$K$3:$K$21,"?*"),"")</f>
         <v/>
       </c>
       <c r="E6" s="7">
-        <f>IFERROR(COUNTIF('Test cases'!$K$3:$K$20,"Y")/COUNTIF('Test cases'!$K$3:$K$20,"?*"),"")</f>
+        <f>IFERROR(COUNTIF('Test cases'!$K$3:$K$21,"Y")/COUNTIF('Test cases'!$K$3:$K$21,"?*"),"")</f>
         <v/>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -842,19 +842,19 @@
         </is>
       </c>
       <c r="B7" s="6">
-        <f>COUNTIFS('Test cases'!$B$3:$B$20,"A: Unstructured",'Test cases'!$L$3:$L$20,"Y")</f>
+        <f>COUNTIFS('Test cases'!$B$3:$B$21,"A: Unstructured",'Test cases'!$L$3:$L$21,"Y")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Test cases'!$B$3:$B$20,"B: Sales",'Test cases'!$L$3:$L$20,"Y")</f>
+        <f>COUNTIFS('Test cases'!$B$3:$B$21,"B: Sales",'Test cases'!$L$3:$L$21,"Y")</f>
         <v/>
       </c>
       <c r="D7" s="6">
-        <f>COUNTIFS('Test cases'!$B$3:$B$20,"Cross-use-case",'Test cases'!$L$3:$L$20,"Y")</f>
+        <f>COUNTIFS('Test cases'!$B$3:$B$21,"Cross-use-case",'Test cases'!$L$3:$L$21,"Y")</f>
         <v/>
       </c>
       <c r="E7" s="6">
-        <f>COUNTIF('Test cases'!$L$3:$L$20,"Y")</f>
+        <f>COUNTIF('Test cases'!$L$3:$L$21,"Y")</f>
         <v/>
       </c>
       <c r="F7" s="6" t="inlineStr">
@@ -870,19 +870,19 @@
         </is>
       </c>
       <c r="B8" s="8">
-        <f>IFERROR(AVERAGEIFS('Test cases'!$M$3:$M$20,'Test cases'!$B$3:$B$20,"A: Unstructured"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Test cases'!$M$3:$M$21,'Test cases'!$B$3:$B$21,"A: Unstructured"),"")</f>
         <v/>
       </c>
       <c r="C8" s="8">
-        <f>IFERROR(AVERAGEIFS('Test cases'!$M$3:$M$20,'Test cases'!$B$3:$B$20,"B: Sales"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Test cases'!$M$3:$M$21,'Test cases'!$B$3:$B$21,"B: Sales"),"")</f>
         <v/>
       </c>
       <c r="D8" s="8">
-        <f>IFERROR(AVERAGEIFS('Test cases'!$M$3:$M$20,'Test cases'!$B$3:$B$20,"Cross-use-case"),"")</f>
+        <f>IFERROR(AVERAGEIFS('Test cases'!$M$3:$M$21,'Test cases'!$B$3:$B$21,"Cross-use-case"),"")</f>
         <v/>
       </c>
       <c r="E8" s="8">
-        <f>IFERROR(AVERAGE('Test cases'!$M$3:$M$20),"")</f>
+        <f>IFERROR(AVERAGE('Test cases'!$M$3:$M$21),"")</f>
         <v/>
       </c>
       <c r="F8" s="6" t="inlineStr">
@@ -909,7 +909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1472,42 +1472,42 @@
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>A9</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>B: Sales</t>
+          <t>A: Unstructured</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Lookup</t>
+          <t>Derived count</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>What discount was given on the Ember Room Heater in April 2026, and why?</t>
+          <t>How many store visits were there per month?</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>25% clearance discount (April and May) to reduce winter stock; standard home comfort discount is 8%.</t>
+          <t>6 store visits, all in August 2026 (12, 14, 18, 20, 22 and 25 August); none in any other month.</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>25%, clearance reason.</t>
+          <t>6 visits, all August.</t>
         </is>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
-          <t>2 = both; 1 = number only; 0 = wrong.</t>
+          <t>2 = 6 in August and none elsewhere; 1 = August only or wrong count; 0 = 'not found' or invented months.</t>
         </is>
       </c>
       <c r="H11" s="12" t="inlineStr">
         <is>
-          <t>Default settings</t>
+          <t>Default settings (found in real testing: an over-strict prompt made the tool answer 'not found')</t>
         </is>
       </c>
       <c r="I11" s="13" t="n"/>
@@ -1520,7 +1520,7 @@
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="B12" s="12" t="inlineStr">
@@ -1530,27 +1530,27 @@
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>Narrative</t>
+          <t>Lookup</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>Why did Drift Air Cooler sales peak in May?</t>
+          <t>What discount was given on the Ember Room Heater in April 2026, and why?</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>A heatwave across North and West India in May (commentary); sales eased from July with the monsoon.</t>
+          <t>25% clearance discount (April and May) to reduce winter stock; standard home comfort discount is 8%.</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>Heatwave, May.</t>
+          <t>25%, clearance reason.</t>
         </is>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
-          <t>2 = cause + timing; 1 = cause only; 0 = wrong.</t>
+          <t>2 = both; 1 = number only; 0 = wrong.</t>
         </is>
       </c>
       <c r="H12" s="12" t="inlineStr">
@@ -1568,7 +1568,7 @@
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>B3</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
@@ -1578,27 +1578,27 @@
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Chart (exact numbers)</t>
+          <t>Narrative</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Plot monthly units sold of Drift Air Cooler as a line chart.</t>
+          <t>Why did Drift Air Cooler sales peak in May?</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Proposal table, then line chart with all regions summed: April 1,095; May 1,469; June 1,150; July 598; August 398; September 323.</t>
+          <t>A heatwave across North and West India in May (commentary); sales eased from July with the monsoon.</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>Values match exactly; source shows Sales_FY27_H1.xlsx sheet Transactions.</t>
+          <t>Heatwave, May.</t>
         </is>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>2 = exact values and plotted after confirm; 1 = right shape, wrong grouping; 0 = wrong numbers.</t>
+          <t>2 = cause + timing; 1 = cause only; 0 = wrong.</t>
         </is>
       </c>
       <c r="H13" s="12" t="inlineStr">
@@ -1616,7 +1616,7 @@
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>B4</t>
+          <t>B3</t>
         </is>
       </c>
       <c r="B14" s="12" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>Bar chart of total net revenue by product for H1.</t>
+          <t>Plot monthly units sold of Drift Air Cooler as a line chart.</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>Bar chart, values (₹): Cascade Water Purifier ₹40,085,016; Drift Air Cooler ₹39,353,430; Breeze Fan ₹30,278,407; Aurora Kettle ₹24,091,861; Flux Mixer Grinder ₹22,321,476; Glow LED Lamp ₹12,884,916; Halo Smart Bulb ₹5,684,360; Ember Room Heater ₹2,909,900. Top: Cascade Water Purifier.</t>
+          <t>Proposal table, then line chart with all regions summed: April 1,095; May 1,469; June 1,150; July 598; August 398; September 323.</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
-          <t>Exact values (page-computed).</t>
+          <t>Values match exactly; source shows Sales_FY27_H1.xlsx sheet Transactions.</t>
         </is>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
-          <t>2 = exact; 0 = otherwise.</t>
+          <t>2 = exact values and plotted after confirm; 1 = right shape, wrong grouping; 0 = wrong numbers.</t>
         </is>
       </c>
       <c r="H14" s="12" t="inlineStr">
@@ -1664,7 +1664,7 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>B5</t>
+          <t>B4</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
@@ -1679,17 +1679,17 @@
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Show net revenue by region as a bar chart.</t>
+          <t>Bar chart of total net revenue by product for H1.</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Values (₹): West ₹50,698,392; North ₹48,128,931; South ₹43,368,264; East ₹35,413,779.</t>
+          <t>Bar chart, values (₹): Cascade Water Purifier ₹40,085,016; Drift Air Cooler ₹39,353,430; Breeze Fan ₹30,278,407; Aurora Kettle ₹24,091,861; Flux Mixer Grinder ₹22,321,476; Glow LED Lamp ₹12,884,916; Halo Smart Bulb ₹5,684,360; Ember Room Heater ₹2,909,900. Top: Cascade Water Purifier.</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
         <is>
-          <t>Exact values.</t>
+          <t>Exact values (page-computed).</t>
         </is>
       </c>
       <c r="G15" s="12" t="inlineStr">
@@ -1712,7 +1712,7 @@
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>B6</t>
+          <t>B5</t>
         </is>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -1722,32 +1722,32 @@
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>Aggregate (text answer)</t>
+          <t>Chart (exact numbers)</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>Which product earned the most net revenue in H1, and how much?</t>
+          <t>Show net revenue by region as a bar chart.</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>Cascade Water Purifier, ₹40,085,016 (₹400.9 lakh).</t>
+          <t>Values (₹): West ₹50,698,392; North ₹48,128,931; South ₹43,368,264; East ₹35,413,779.</t>
         </is>
       </c>
       <c r="F16" s="12" t="inlineStr">
         <is>
-          <t>Product name and amount within 1%.</t>
+          <t>Exact values.</t>
         </is>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
-          <t>2 = right product and amount; 1 = right product, wrong/missing amount, or says it can only see part of the data; 0 = wrong product stated confidently.</t>
+          <t>2 = exact; 0 = otherwise.</t>
         </is>
       </c>
       <c r="H16" s="12" t="inlineStr">
         <is>
-          <t>Default settings; check the 'Exact figures calculated by the page' table under the answer</t>
+          <t>Default settings</t>
         </is>
       </c>
       <c r="I16" s="13" t="n"/>
@@ -1760,7 +1760,7 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>B7</t>
+          <t>B6</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
@@ -1775,27 +1775,27 @@
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>What was total net revenue for H1 across all products and regions?</t>
+          <t>Which product earned the most net revenue in H1, and how much?</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>₹177,609,366 (₹1,776.1 lakh).</t>
+          <t>Cascade Water Purifier, ₹40,085,016 (₹400.9 lakh).</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>Within 1%, or an honest statement that the full total can't be computed from the passages it sees.</t>
+          <t>Product name and amount within 1%.</t>
         </is>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>2 = correct; 1 = honest 'can't compute all rows'; 0 = a wrong number stated as fact.</t>
+          <t>2 = right product and amount; 1 = right product, wrong/missing amount, or says it can only see part of the data; 0 = wrong product stated confidently.</t>
         </is>
       </c>
       <c r="H17" s="12" t="inlineStr">
         <is>
-          <t>Default settings; check the calculated table under the answer</t>
+          <t>Default settings; check the 'Exact figures calculated by the page' table under the answer</t>
         </is>
       </c>
       <c r="I17" s="13" t="n"/>
@@ -1808,7 +1808,7 @@
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>B8</t>
+          <t>B7</t>
         </is>
       </c>
       <c r="B18" s="12" t="inlineStr">
@@ -1823,22 +1823,22 @@
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>Which products missed their H1 unit target?</t>
+          <t>What was total net revenue for H1 across all products and regions?</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>Missed: Cascade Water Purifier (3,246 vs target 3,700), Ember Room Heater (1,145 vs target 1,400), Flux Mixer Grinder (5,109 vs target 5,400), Halo Smart Bulb (4,890 vs target 6,400).</t>
+          <t>₹177,609,366 (₹1,776.1 lakh).</t>
         </is>
       </c>
       <c r="F18" s="12" t="inlineStr">
         <is>
-          <t>Exactly these products.</t>
+          <t>Within 1%, or an honest statement that the full total can't be computed from the passages it sees.</t>
         </is>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
-          <t>2 = exact list; 1 = partial or honest limitation; 0 = wrong list stated as fact.</t>
+          <t>2 = correct; 1 = honest 'can't compute all rows'; 0 = a wrong number stated as fact.</t>
         </is>
       </c>
       <c r="H18" s="12" t="inlineStr">
@@ -1856,7 +1856,7 @@
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>B9</t>
+          <t>B8</t>
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr">
@@ -1866,32 +1866,32 @@
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Summary</t>
+          <t>Aggregate (text answer)</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Summarise how the Halo Smart Bulb has done since launch.</t>
+          <t>Which products missed their H1 unit target?</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Launched June 2026 with a 15% introductory discount; units grew every month (June 501; July 1,078; August 1,513; September 1,798); app pairing problems reported by customers and stores; app fix in progress.</t>
+          <t>Missed: Cascade Water Purifier (3,246 vs target 3,700), Ember Room Heater (1,145 vs target 1,400), Flux Mixer Grinder (5,109 vs target 5,400), Halo Smart Bulb (4,890 vs target 6,400).</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>Launch month, discount, growth, pairing issue.</t>
+          <t>Exactly these products.</t>
         </is>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>2 = all four; 1 = two or three; 0 = otherwise.</t>
+          <t>2 = exact list; 1 = partial or honest limitation; 0 = wrong list stated as fact.</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
         <is>
-          <t>Default settings</t>
+          <t>Default settings; check the calculated table under the answer</t>
         </is>
       </c>
       <c r="I19" s="13" t="n"/>
@@ -1904,7 +1904,7 @@
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>B10</t>
+          <t>B9</t>
         </is>
       </c>
       <c r="B20" s="12" t="inlineStr">
@@ -1914,27 +1914,27 @@
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>Negative (not in documents)</t>
+          <t>Summary</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>What were sales in October 2026?</t>
+          <t>Summarise how the Halo Smart Bulb has done since launch.</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>Not in the data (the data covers April to September 2026). Should say it couldn't find this.</t>
+          <t>Launched June 2026 with a 15% introductory discount; units grew every month (June 501; July 1,078; August 1,513; September 1,798); app pairing problems reported by customers and stores; app fix in progress.</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
         <is>
-          <t>Must not invent October figures.</t>
+          <t>Launch month, discount, growth, pairing issue.</t>
         </is>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
-          <t>2 = says not found / data ends September; 0 = any invented figure.</t>
+          <t>2 = all four; 1 = two or three; 0 = otherwise.</t>
         </is>
       </c>
       <c r="H20" s="12" t="inlineStr">
@@ -1949,13 +1949,61 @@
       <c r="M20" s="13" t="n"/>
       <c r="N20" s="13" t="n"/>
     </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>B10</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>B: Sales</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>Negative (not in documents)</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>What were sales in October 2026?</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>Not in the data (the data covers April to September 2026). Should say it couldn't find this.</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="inlineStr">
+        <is>
+          <t>Must not invent October figures.</t>
+        </is>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>2 = says not found / data ends September; 0 = any invented figure.</t>
+        </is>
+      </c>
+      <c r="H21" s="12" t="inlineStr">
+        <is>
+          <t>Default settings</t>
+        </is>
+      </c>
+      <c r="I21" s="13" t="n"/>
+      <c r="J21" s="13" t="n"/>
+      <c r="K21" s="13" t="n"/>
+      <c r="L21" s="13" t="n"/>
+      <c r="M21" s="13" t="n"/>
+      <c r="N21" s="13" t="n"/>
+    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="J3:J20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
+    <dataValidation sqref="J3:J21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
       <formula1>0</formula1>
       <formula2>2</formula2>
     </dataValidation>
-    <dataValidation sqref="K3:L20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K3:L21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Y,N"</formula1>
     </dataValidation>
   </dataValidations>

--- a/local-qa/eval/Evaluation_Scoresheet.xlsx
+++ b/local-qa/eval/Evaluation_Scoresheet.xlsx
@@ -1444,17 +1444,17 @@
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>Not in the documents. The tool should answer that it couldn't find this.</t>
+          <t>Not in the documents. The tool should say it couldn't find this, with a 'How I checked' table giving each of the documents and why it can't answer.</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>Must not invent anything.</t>
+          <t>Must not invent anything; every document checked.</t>
         </is>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
-          <t>2 = says not found; 0 = any invented content.</t>
+          <t>2 = not found with a check per document; 1 = not found without the checks; 0 = any invented content.</t>
         </is>
       </c>
       <c r="H10" s="12" t="inlineStr">
